--- a/AAII_Financials/Quarterly/VRPX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VRPX_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
   <si>
     <t>VRPX</t>
   </si>
@@ -656,87 +656,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43830</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43646</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
@@ -749,8 +750,11 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -811,8 +815,11 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -873,8 +880,11 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -935,8 +945,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,56 +972,57 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E12" s="3">
         <v>1300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2800</v>
-      </c>
-      <c r="H12" s="3">
-        <v>3300</v>
       </c>
       <c r="I12" s="3">
         <v>3300</v>
       </c>
       <c r="J12" s="3">
-        <v>1700</v>
+        <v>3300</v>
       </c>
       <c r="K12" s="3">
         <v>1700</v>
       </c>
       <c r="L12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M12" s="3">
         <v>300</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>200</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1021,8 +1035,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,8 +1100,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1136,8 +1156,8 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
@@ -1145,8 +1165,11 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1207,8 +1230,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,56 +1254,57 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E17" s="3">
         <v>3200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3200</v>
-      </c>
-      <c r="L17" s="3">
-        <v>2300</v>
       </c>
       <c r="M17" s="3">
         <v>2300</v>
       </c>
       <c r="N17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="O17" s="3">
         <v>4200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1500</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1290,8 +1317,11 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1299,47 +1329,47 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-1700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-7700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-5900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-5100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3200</v>
-      </c>
-      <c r="L18" s="3">
-        <v>-2300</v>
       </c>
       <c r="M18" s="3">
         <v>-2300</v>
       </c>
       <c r="N18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="O18" s="3">
         <v>-4200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-1500</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1352,8 +1382,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,8 +1409,9 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1394,7 +1428,7 @@
         <v>100</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
@@ -1403,11 +1437,11 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1423,8 +1457,8 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
+      <c r="R20" s="3">
+        <v>0</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
@@ -1438,8 +1472,11 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1447,11 +1484,11 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1500</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1500,8 +1537,11 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1511,8 +1551,8 @@
       <c r="E22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
@@ -1523,11 +1563,11 @@
       <c r="I22" s="3">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1536,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="N22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O22" s="3">
         <v>100</v>
@@ -1547,8 +1587,8 @@
       <c r="Q22" s="3">
         <v>100</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
+      <c r="R22" s="3">
+        <v>100</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
@@ -1562,56 +1602,59 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-5100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-4100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-2400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-1600</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1624,8 +1667,11 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1686,8 +1732,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,56 +1797,59 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-7600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1600</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1810,56 +1862,59 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-7600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-2300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-2400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1600</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1872,8 +1927,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,8 +2187,11 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2138,7 +2208,7 @@
         <v>-100</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
@@ -2147,11 +2217,11 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2167,8 +2237,8 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
+      <c r="R32" s="3">
+        <v>0</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
@@ -2182,56 +2252,59 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-7600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-2300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-2400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1600</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2244,8 +2317,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,56 +2382,59 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-7600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-2300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-2400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1600</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2368,61 +2447,64 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43830</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43646</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2435,8 +2517,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,50 +2569,51 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E41" s="3">
         <v>14800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>17000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>19000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>26100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>30800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>36800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>41700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>10500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>400</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,8 +2632,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2607,8 +2697,11 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2646,11 +2739,11 @@
         <v>0</v>
       </c>
       <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
         <v>400</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2669,8 +2762,11 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2731,49 +2827,52 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>900</v>
+      </c>
+      <c r="E45" s="3">
         <v>1100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1000</v>
       </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
+      <c r="P45" s="3">
+        <v>0</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
@@ -2793,50 +2892,53 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E46" s="3">
         <v>16000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>18500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>23600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>29400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>34700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>39600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>43300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>800</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2855,8 +2957,11 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2917,8 +3022,11 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2979,8 +3087,11 @@
       <c r="V48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3041,8 +3152,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,8 +3282,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3194,21 +3314,21 @@
       <c r="K52" s="3">
         <v>0</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3">
-        <v>0</v>
+      <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N52" s="3">
+        <v>0</v>
+      </c>
+      <c r="O52" s="3">
         <v>400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>100</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3227,8 +3347,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,50 +3412,53 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E54" s="3">
         <v>16000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>18500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>19700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>23600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>29400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>34700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>39600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>43300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>13200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>900</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3477,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,8 +3529,9 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3413,23 +3544,23 @@
       <c r="F57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G57" s="3">
+      <c r="G57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3">
         <v>2000</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3">
+        <v>0</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
@@ -3446,8 +3577,8 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
+      <c r="R57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
@@ -3461,8 +3592,11 @@
       <c r="V57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3491,20 +3625,20 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M58" s="3">
         <v>100</v>
       </c>
       <c r="N58" s="3">
+        <v>100</v>
+      </c>
+      <c r="O58" s="3">
         <v>500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1500</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3523,50 +3657,53 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E59" s="3">
         <v>3600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2100</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3585,50 +3722,53 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E60" s="3">
         <v>3600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>4200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3500</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,8 +3787,11 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3677,7 +3820,7 @@
         <v>0</v>
       </c>
       <c r="L61" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="M61" s="3">
         <v>1000</v>
@@ -3686,7 +3829,7 @@
         <v>1000</v>
       </c>
       <c r="O61" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="P61" s="3">
         <v>0</v>
@@ -3709,8 +3852,11 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3771,8 +3917,11 @@
       <c r="V62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,50 +4112,53 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E66" s="3">
         <v>3600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3600</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4019,8 +4177,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4229,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,50 +4462,53 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-49000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-45900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-44400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-41400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-33700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-27800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-22700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-18600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-15400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-13000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-10600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-8200</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4353,8 +4527,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,50 +4722,53 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E76" s="3">
         <v>12300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>15200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>19400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>26900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>32600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>37500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>41500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>9600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-4200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-2700</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4601,8 +4787,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,61 +4852,64 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43830</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43646</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4730,56 +4922,59 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-7600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-2300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-2400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1600</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4792,8 +4987,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,8 +5014,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4878,8 +5077,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,50 +5402,53 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-3100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-600</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5250,8 +5467,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,8 +5494,9 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5336,8 +5557,11 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,8 +5687,11 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5522,8 +5752,11 @@
       <c r="V94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,8 +5779,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5608,8 +5842,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,8 +6037,11 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5805,8 +6051,8 @@
       <c r="E100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G100" s="3">
         <v>0</v>
@@ -5818,26 +6064,26 @@
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>36000</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>15300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1000</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5856,8 +6102,11 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5918,50 +6167,53 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>31200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>12200</v>
       </c>
-      <c r="N102" s="3">
-        <v>0</v>
-      </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>400</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5978,6 +6230,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VRPX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VRPX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
   <si>
     <t>VRPX</t>
   </si>
@@ -656,94 +656,95 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43646</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -753,8 +754,14 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -818,8 +825,14 @@
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -883,8 +896,14 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -948,8 +967,14 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -973,62 +998,64 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F12" s="3">
         <v>1500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>1300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>1200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>1400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>2800</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>3300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>3300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>1700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>1700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>1100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>1300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="S12" s="3">
         <v>600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="T12" s="3">
         <v>200</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1038,8 +1065,14 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1103,8 +1136,14 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1159,17 +1198,23 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1233,8 +1278,14 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1255,62 +1306,64 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F17" s="3">
         <v>6100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>3200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>3100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>7700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>5900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>5100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>3200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>2300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>2300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>4200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>3200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1500</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1320,8 +1373,14 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1329,53 +1388,53 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="G18" s="3">
         <v>-3200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-1700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-3100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-7700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-5900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-5100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-4100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-3200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-2300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-2300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-4200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-3200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-1500</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1385,8 +1444,14 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1410,8 +1475,10 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1431,23 +1498,23 @@
         <v>100</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1460,11 +1527,11 @@
       <c r="R20" s="3">
         <v>0</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
@@ -1475,26 +1542,32 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E21" s="3">
+      <c r="E21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="G21" s="3">
         <v>-3100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-1500</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1540,8 +1613,14 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1554,11 +1633,11 @@
       <c r="F22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I22" s="3">
         <v>0</v>
@@ -1566,23 +1645,23 @@
       <c r="J22" s="3">
         <v>0</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
+      <c r="K22" s="3">
+        <v>0</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
       <c r="O22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="3">
         <v>100</v>
@@ -1590,11 +1669,11 @@
       <c r="R22" s="3">
         <v>100</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
+      <c r="S22" s="3">
+        <v>100</v>
+      </c>
+      <c r="T22" s="3">
+        <v>100</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
@@ -1605,62 +1684,68 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F23" s="3">
         <v>-6000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-3100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-1500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-3000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-7600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-5900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-5100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-4100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-3200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-2300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-2400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-4300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-3300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-1600</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1670,8 +1755,14 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1735,8 +1826,14 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1800,62 +1897,68 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F26" s="3">
         <v>-6000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-3100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-1500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-3000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-7600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-5900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-5100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-4100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-3200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-2300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-2400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-4300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-3300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-1600</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1865,62 +1968,68 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F27" s="3">
         <v>-6000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-3100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-1500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-3000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-7600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-5900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-5100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-4100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-3200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-2400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-4300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-3300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-1600</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1930,8 +2039,14 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1995,8 +2110,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2060,8 +2181,14 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2125,8 +2252,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2190,8 +2323,14 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2211,23 +2350,23 @@
         <v>-100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -2240,11 +2379,11 @@
       <c r="R32" s="3">
         <v>0</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
@@ -2255,62 +2394,68 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F33" s="3">
         <v>-6000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-3100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-1500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-3000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-7600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-5900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-5100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-4100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-3200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-2300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-2400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-4300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-3300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-1600</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2320,8 +2465,14 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2385,62 +2536,68 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F35" s="3">
         <v>-6000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-3100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-1500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-3000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-7600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-5900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-5100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-4100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-3200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-2300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-2400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-4300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-3300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-1600</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2450,67 +2607,73 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43646</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2520,8 +2683,14 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2545,8 +2714,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2570,56 +2741,58 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>9100</v>
+      </c>
+      <c r="F41" s="3">
         <v>12200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>14800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>17000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>19000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>20600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>26100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>30800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>36800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>41700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>10500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>12300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>400</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2635,8 +2808,14 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2700,8 +2879,14 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2742,14 +2927,14 @@
         <v>0</v>
       </c>
       <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3">
         <v>400</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2765,8 +2950,14 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2830,55 +3021,61 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>500</v>
+      </c>
+      <c r="F45" s="3">
         <v>900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>3100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>3300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>3900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>2700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1000</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3">
+        <v>0</v>
       </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
@@ -2895,56 +3092,62 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>9600</v>
+      </c>
+      <c r="F46" s="3">
         <v>13000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>16000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>18500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>19700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>23600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>29400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>34700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>39600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>43300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>11400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>13200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>800</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2960,8 +3163,14 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3025,8 +3234,14 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3090,8 +3305,14 @@
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3155,8 +3376,14 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3220,8 +3447,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3285,8 +3518,14 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3317,24 +3556,24 @@
       <c r="L52" s="3">
         <v>0</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
+      <c r="M52" s="3">
+        <v>0</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3">
         <v>400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>100</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,8 +3589,14 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3415,56 +3660,62 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>9600</v>
+      </c>
+      <c r="F54" s="3">
         <v>13000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>16000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>18500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>19700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>23600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>29400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>34700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>39600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>43300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>11400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>13200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>900</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3480,8 +3731,14 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3505,8 +3762,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3530,43 +3789,45 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
+      <c r="D57" s="3">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3">
+        <v>0</v>
+      </c>
+      <c r="F57" s="3">
+        <v>0</v>
+      </c>
+      <c r="G57" s="3">
+        <v>0</v>
       </c>
       <c r="H57" s="3">
-        <v>2000</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
+        <v>0</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
+      <c r="L57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
+      <c r="N57" s="3">
+        <v>0</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
@@ -3580,11 +3841,11 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
-      <c r="T57" s="3">
-        <v>0</v>
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U57" s="3">
         <v>0</v>
@@ -3595,8 +3856,14 @@
       <c r="W57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3628,23 +3895,23 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1500</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3660,56 +3927,62 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F59" s="3">
         <v>6500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>3600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>3300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>3100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
+        <v>4200</v>
+      </c>
+      <c r="K59" s="3">
+        <v>2500</v>
+      </c>
+      <c r="L59" s="3">
         <v>2200</v>
       </c>
-      <c r="I59" s="3">
-        <v>2500</v>
-      </c>
-      <c r="J59" s="3">
-        <v>2200</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>2800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>2600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>3100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2100</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3725,56 +3998,62 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F60" s="3">
         <v>6500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>4200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>2500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>2200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>2100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>2800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>2600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>3700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>3500</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3790,8 +4069,14 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3823,19 +4108,19 @@
         <v>0</v>
       </c>
       <c r="M61" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="N61" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="O61" s="3">
         <v>1000</v>
       </c>
       <c r="P61" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Q61" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="R61" s="3">
         <v>0</v>
@@ -3855,8 +4140,14 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3920,8 +4211,14 @@
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3985,8 +4282,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4050,8 +4353,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4115,56 +4424,62 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F66" s="3">
         <v>6500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>4200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>2500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>2200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>2100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>3900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>4700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>3600</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4180,8 +4495,14 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4205,8 +4526,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4270,8 +4593,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4335,8 +4664,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4400,8 +4735,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4465,56 +4806,62 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-62800</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-59500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-55000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-49000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-45900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-44400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-41400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-33700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-27800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-22700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-18600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-15400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-13000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-10600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4530,8 +4877,14 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4595,8 +4948,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4660,8 +5019,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4725,56 +5090,62 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F76" s="3">
         <v>6500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>12300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>15200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>16600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>19400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>26900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>32600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>37500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>41500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>7500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>9600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-4200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4790,8 +5161,14 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4855,67 +5232,73 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43646</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4925,62 +5308,68 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F81" s="3">
         <v>-6000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-3100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-1500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-3000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-7600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-5900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-5100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-4100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-3200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-2300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-2400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-4300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-3300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-1600</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4990,8 +5379,14 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5015,8 +5410,10 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5080,8 +5477,14 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5145,8 +5548,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5210,8 +5619,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5275,8 +5690,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5340,8 +5761,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5405,56 +5832,62 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F89" s="3">
         <v>-2700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-2200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-2000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-5500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-4700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-6000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-4900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-4700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-3100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-1400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-600</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5470,8 +5903,14 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5495,8 +5934,10 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5560,8 +6001,14 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5625,8 +6072,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5690,8 +6143,14 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5755,8 +6214,14 @@
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5780,8 +6245,10 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5845,8 +6312,14 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5910,8 +6383,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5975,8 +6454,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6040,13 +6525,19 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>500</v>
       </c>
       <c r="E100" s="3" t="s">
         <v>3</v>
@@ -6054,11 +6545,11 @@
       <c r="F100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I100" s="3">
         <v>0</v>
@@ -6067,29 +6558,29 @@
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
+      </c>
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>36000</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>15300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>1400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>1000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6105,8 +6596,14 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6170,56 +6667,62 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-2700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-2200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-2000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-1600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-5500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-4700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-6000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-4900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>31200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-1800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>12200</v>
       </c>
-      <c r="O102" s="3">
-        <v>0</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
         <v>400</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6233,6 +6736,12 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VRPX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VRPX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="92">
   <si>
     <t>VRPX</t>
   </si>
@@ -656,98 +656,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -760,8 +761,11 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -831,8 +835,11 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -902,8 +909,11 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -973,8 +983,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1000,65 +1013,66 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E12" s="3">
         <v>1600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2800</v>
-      </c>
-      <c r="K12" s="3">
-        <v>3300</v>
       </c>
       <c r="L12" s="3">
         <v>3300</v>
       </c>
       <c r="M12" s="3">
-        <v>1700</v>
+        <v>3300</v>
       </c>
       <c r="N12" s="3">
         <v>1700</v>
       </c>
       <c r="O12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="P12" s="3">
         <v>300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>200</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1071,8 +1085,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1142,8 +1159,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1204,8 +1224,8 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
@@ -1213,8 +1233,11 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1284,8 +1307,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1308,65 +1334,66 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E17" s="3">
         <v>3300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3200</v>
-      </c>
-      <c r="O17" s="3">
-        <v>2300</v>
       </c>
       <c r="P17" s="3">
         <v>2300</v>
       </c>
       <c r="Q17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="R17" s="3">
         <v>4200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1500</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1379,8 +1406,11 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1388,56 +1418,56 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-4700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-6100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-1700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-5900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-3200</v>
-      </c>
-      <c r="O18" s="3">
-        <v>-2300</v>
       </c>
       <c r="P18" s="3">
         <v>-2300</v>
       </c>
       <c r="Q18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="R18" s="3">
         <v>-4200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-1800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-3200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1500</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1450,8 +1480,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,8 +1510,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1504,7 +1538,7 @@
         <v>100</v>
       </c>
       <c r="K20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
@@ -1513,11 +1547,11 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1533,8 +1567,8 @@
       <c r="T20" s="3">
         <v>0</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
+      <c r="U20" s="3">
+        <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
@@ -1548,29 +1582,32 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="3">
+      <c r="E21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21" s="3">
         <v>-6000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-3100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-1500</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1619,13 +1656,16 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>3</v>
@@ -1639,8 +1679,8 @@
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I22" s="3">
-        <v>0</v>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J22" s="3">
         <v>0</v>
@@ -1651,11 +1691,11 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1664,7 +1704,7 @@
         <v>0</v>
       </c>
       <c r="Q22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R22" s="3">
         <v>100</v>
@@ -1675,8 +1715,8 @@
       <c r="T22" s="3">
         <v>100</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
+      <c r="U22" s="3">
+        <v>100</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
@@ -1690,65 +1730,68 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-6000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-3100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-7600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-1900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1600</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1761,8 +1804,11 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1832,8 +1878,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1903,65 +1952,68 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-3100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-4100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-4300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1600</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1974,65 +2026,68 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-6000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-3100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-7600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-5900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-4100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-4300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1600</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2045,8 +2100,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2116,8 +2174,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2187,8 +2248,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2258,8 +2322,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2329,8 +2396,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2356,7 +2426,7 @@
         <v>-100</v>
       </c>
       <c r="K32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
@@ -2365,11 +2435,11 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2385,8 +2455,8 @@
       <c r="T32" s="3">
         <v>0</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
+      <c r="U32" s="3">
+        <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
@@ -2400,65 +2470,68 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-6000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-3100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-7600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-5900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-4300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1600</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2471,8 +2544,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2542,65 +2618,68 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-6000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-3100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-7600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-5900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-4300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1600</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2613,70 +2692,73 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2689,8 +2771,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2716,8 +2801,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2743,8 +2829,9 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2752,50 +2839,50 @@
         <v>1900</v>
       </c>
       <c r="E41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F41" s="3">
         <v>9100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>14800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>17000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>19000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>20600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>26100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>30800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>36800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>41700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>12300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>400</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2814,8 +2901,11 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2885,8 +2975,11 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2933,11 +3026,11 @@
         <v>0</v>
       </c>
       <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
         <v>400</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2956,8 +3049,11 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3027,58 +3123,61 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>700</v>
+      </c>
+      <c r="E45" s="3">
         <v>1300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
+      <c r="S45" s="3">
+        <v>0</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
@@ -3098,59 +3197,62 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E46" s="3">
         <v>3100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>18500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>19700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>23600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>29400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>34700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>39600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>43300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>11400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>13200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>800</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3169,8 +3271,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3240,8 +3345,11 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3311,8 +3419,11 @@
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3382,8 +3493,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3453,8 +3567,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3524,8 +3641,11 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3562,21 +3682,21 @@
       <c r="N52" s="3">
         <v>0</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3">
-        <v>0</v>
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3">
         <v>400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>100</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3595,8 +3715,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3666,59 +3789,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E54" s="3">
         <v>3100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>18500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>19700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>23600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>29400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>34700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>39600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>43300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>11400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>13200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>900</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3737,8 +3863,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3764,8 +3893,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3791,8 +3921,9 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3817,8 +3948,8 @@
       <c r="J57" s="3">
         <v>0</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
+      <c r="K57" s="3">
+        <v>0</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
@@ -3826,11 +3957,11 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N57" s="3">
-        <v>0</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3">
+        <v>0</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
@@ -3847,8 +3978,8 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
+      <c r="U57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V57" s="3">
         <v>0</v>
@@ -3862,8 +3993,11 @@
       <c r="Y57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3901,20 +4035,20 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P58" s="3">
         <v>100</v>
       </c>
       <c r="Q58" s="3">
+        <v>100</v>
+      </c>
+      <c r="R58" s="3">
         <v>500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1500</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3933,59 +4067,62 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E59" s="3">
         <v>4300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2100</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4004,59 +4141,62 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E60" s="3">
         <v>4300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>4200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3500</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4075,8 +4215,11 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4114,7 +4257,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="P61" s="3">
         <v>1000</v>
@@ -4123,7 +4266,7 @@
         <v>1000</v>
       </c>
       <c r="R61" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="S61" s="3">
         <v>0</v>
@@ -4146,8 +4289,11 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4217,8 +4363,11 @@
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4288,8 +4437,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4359,8 +4511,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4430,59 +4585,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E66" s="3">
         <v>4300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3600</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4501,8 +4659,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4528,8 +4689,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4599,8 +4761,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4670,8 +4835,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4741,8 +4909,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4812,59 +4983,62 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-66200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-62800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-59500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-55000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-49000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-45900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-44400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-41400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-33700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-27800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-22700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-18600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-15400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-10600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-8200</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4883,8 +5057,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4954,8 +5131,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5025,8 +5205,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5096,59 +5279,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>26900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>32600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>37500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>41500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>9600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-4200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-2700</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5167,8 +5353,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5238,70 +5427,73 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5314,65 +5506,68 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-6000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-3100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-7600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-5900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-4300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1600</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5385,8 +5580,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5412,8 +5610,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5483,8 +5682,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5554,8 +5756,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5625,8 +5830,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5696,8 +5904,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5767,8 +5978,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5838,59 +6052,62 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-3000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-600</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5909,8 +6126,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5936,8 +6156,9 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6007,8 +6228,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6078,8 +6302,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6149,8 +6376,11 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6220,8 +6450,11 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6247,8 +6480,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6318,8 +6552,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6389,8 +6626,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6460,8 +6700,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6531,17 +6774,20 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E100" s="3">
         <v>500</v>
       </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6551,8 +6797,8 @@
       <c r="H100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J100" s="3">
         <v>0</v>
@@ -6564,26 +6810,26 @@
         <v>0</v>
       </c>
       <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>36000</v>
       </c>
-      <c r="O100" s="3">
-        <v>0</v>
-      </c>
       <c r="P100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q100" s="3">
         <v>15300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1000</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6602,8 +6848,11 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6673,59 +6922,62 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-7300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-4700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>31200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>12200</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>400</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6742,6 +6994,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VRPX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VRPX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="92">
   <si>
     <t>VRPX</t>
   </si>
@@ -656,102 +656,103 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
@@ -764,31 +765,34 @@
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -838,8 +842,11 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -912,8 +919,11 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -986,8 +996,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1014,68 +1027,69 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E12" s="3">
         <v>2000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>2800</v>
-      </c>
-      <c r="L12" s="3">
-        <v>3300</v>
       </c>
       <c r="M12" s="3">
         <v>3300</v>
       </c>
       <c r="N12" s="3">
-        <v>1700</v>
+        <v>3300</v>
       </c>
       <c r="O12" s="3">
         <v>1700</v>
       </c>
       <c r="P12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q12" s="3">
         <v>300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>1100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>200</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1088,8 +1102,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1162,31 +1179,34 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
+        <v>3800</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-1300</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1227,8 +1247,8 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
@@ -1236,8 +1256,11 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1310,8 +1333,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1335,68 +1361,69 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E17" s="3">
         <v>3500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3300</v>
       </c>
-      <c r="F17" s="3">
-        <v>4700</v>
-      </c>
       <c r="G17" s="3">
+        <v>900</v>
+      </c>
+      <c r="H17" s="3">
         <v>6100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3200</v>
       </c>
-      <c r="I17" s="3">
-        <v>1700</v>
-      </c>
       <c r="J17" s="3">
+        <v>2900</v>
+      </c>
+      <c r="K17" s="3">
         <v>3100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3200</v>
-      </c>
-      <c r="P17" s="3">
-        <v>2300</v>
       </c>
       <c r="Q17" s="3">
         <v>2300</v>
       </c>
       <c r="R17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="S17" s="3">
         <v>4200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1500</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1409,68 +1436,71 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-1900</v>
       </c>
       <c r="E18" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="F18" s="3">
         <v>-3300</v>
       </c>
-      <c r="F18" s="3">
-        <v>-4700</v>
-      </c>
       <c r="G18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H18" s="3">
         <v>-6100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-3200</v>
       </c>
-      <c r="I18" s="3">
-        <v>-1700</v>
-      </c>
       <c r="J18" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="K18" s="3">
         <v>-3100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-5900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-3200</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-2300</v>
       </c>
       <c r="Q18" s="3">
         <v>-2300</v>
       </c>
       <c r="R18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="S18" s="3">
         <v>-4200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-3200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1500</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1483,8 +1513,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1511,37 +1544,38 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="G20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="H20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="K20" s="3">
         <v>100</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1550,11 +1584,11 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1570,8 +1604,8 @@
       <c r="U20" s="3">
         <v>0</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
+      <c r="V20" s="3">
+        <v>0</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
@@ -1585,31 +1619,34 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-1900</v>
       </c>
       <c r="E21" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F21" s="3">
         <v>-3200</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="H21" s="3">
         <v>-6000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-3100</v>
       </c>
-      <c r="I21" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+      <c r="J21" s="3">
+        <v>-2800</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1659,16 +1696,19 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>3</v>
@@ -1682,8 +1722,8 @@
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1694,11 +1734,11 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1707,7 +1747,7 @@
         <v>0</v>
       </c>
       <c r="R22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S22" s="3">
         <v>100</v>
@@ -1718,8 +1758,8 @@
       <c r="U22" s="3">
         <v>100</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
+      <c r="V22" s="3">
+        <v>100</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
@@ -1733,68 +1773,71 @@
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-3500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-6000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-7600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-5900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-4300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1600</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1807,31 +1850,34 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1881,8 +1927,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1955,68 +2004,71 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-3500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-6000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-3100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-3000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-4100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-4300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-3300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1600</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2029,68 +2081,71 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-3500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-3100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-3000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-5900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-4100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-4300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-3300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1600</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2103,8 +2158,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2177,8 +2235,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2251,8 +2312,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2325,8 +2389,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2399,37 +2466,40 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="G32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="H32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="K32" s="3">
         <v>-100</v>
       </c>
       <c r="L32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -2438,11 +2508,11 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -2458,8 +2528,8 @@
       <c r="U32" s="3">
         <v>0</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
+      <c r="V32" s="3">
+        <v>0</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
@@ -2473,68 +2543,71 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-3500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-3100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-3000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-5900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-4300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-3300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1600</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2547,8 +2620,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2621,68 +2697,71 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-3500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-3100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-3000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-5900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-4300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-3300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1600</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2695,73 +2774,76 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2774,8 +2856,11 @@
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2802,8 +2887,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2830,62 +2916,63 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="E41" s="3">
         <v>1900</v>
       </c>
       <c r="F41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="G41" s="3">
         <v>9100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>14800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>17000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>19000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>20600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>26100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>30800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>36800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>41700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>10500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>12300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>400</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2904,8 +2991,11 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2978,31 +3068,34 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3029,11 +3122,11 @@
         <v>0</v>
       </c>
       <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
         <v>400</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3052,31 +3145,34 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3126,61 +3222,64 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>1300</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
         <v>500</v>
       </c>
       <c r="G45" s="3">
+        <v>300</v>
+      </c>
+      <c r="H45" s="3">
+        <v>400</v>
+      </c>
+      <c r="I45" s="3">
+        <v>400</v>
+      </c>
+      <c r="J45" s="3">
+        <v>500</v>
+      </c>
+      <c r="K45" s="3">
+        <v>700</v>
+      </c>
+      <c r="L45" s="3">
+        <v>3100</v>
+      </c>
+      <c r="M45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="N45" s="3">
+        <v>3900</v>
+      </c>
+      <c r="O45" s="3">
+        <v>2700</v>
+      </c>
+      <c r="P45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="Q45" s="3">
         <v>900</v>
       </c>
-      <c r="H45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1500</v>
-      </c>
-      <c r="J45" s="3">
-        <v>700</v>
-      </c>
-      <c r="K45" s="3">
-        <v>3100</v>
-      </c>
-      <c r="L45" s="3">
-        <v>3300</v>
-      </c>
-      <c r="M45" s="3">
-        <v>3900</v>
-      </c>
-      <c r="N45" s="3">
-        <v>2700</v>
-      </c>
-      <c r="O45" s="3">
-        <v>1600</v>
-      </c>
-      <c r="P45" s="3">
-        <v>900</v>
-      </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1000</v>
       </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
       <c r="S45" s="3">
         <v>0</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
+      <c r="T45" s="3">
+        <v>0</v>
       </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
@@ -3200,62 +3299,65 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>300</v>
+      </c>
+      <c r="E46" s="3">
         <v>2600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>16000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>19700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>23600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>29400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>34700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>39600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>43300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>11400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>13200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>800</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3274,31 +3376,34 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3348,31 +3453,34 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>0</v>
-      </c>
-      <c r="E48" s="3">
-        <v>0</v>
-      </c>
-      <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3">
-        <v>0</v>
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K48" s="3">
         <v>0</v>
@@ -3422,8 +3530,11 @@
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3496,8 +3607,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3570,8 +3684,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3644,31 +3761,34 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>0</v>
-      </c>
-      <c r="E52" s="3">
-        <v>0</v>
-      </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
-        <v>0</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -3685,21 +3805,21 @@
       <c r="O52" s="3">
         <v>0</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>0</v>
+      <c r="P52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R52" s="3">
+        <v>0</v>
+      </c>
+      <c r="S52" s="3">
         <v>400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>100</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3718,8 +3838,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3792,62 +3915,65 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>300</v>
+      </c>
+      <c r="E54" s="3">
         <v>2600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>18500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>19700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>23600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>29400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>34700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>39600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>43300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>11400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>13200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>900</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,8 +3992,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3894,8 +4023,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3922,16 +4052,17 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F57" s="3">
         <v>0</v>
@@ -3943,7 +4074,7 @@
         <v>0</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J57" s="3">
         <v>0</v>
@@ -3951,8 +4082,8 @@
       <c r="K57" s="3">
         <v>0</v>
       </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
+      <c r="L57" s="3">
+        <v>0</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
@@ -3960,11 +4091,11 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3">
+        <v>0</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
@@ -3981,8 +4112,8 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W57" s="3">
         <v>0</v>
@@ -3996,8 +4127,11 @@
       <c r="Z57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4038,20 +4172,20 @@
         <v>0</v>
       </c>
       <c r="P58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="3">
         <v>100</v>
       </c>
       <c r="R58" s="3">
+        <v>100</v>
+      </c>
+      <c r="S58" s="3">
         <v>500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1500</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4070,62 +4204,65 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>5400</v>
+      <c r="D59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E59" s="3">
-        <v>4300</v>
+        <v>2500</v>
       </c>
       <c r="F59" s="3">
-        <v>7700</v>
+        <v>2500</v>
       </c>
       <c r="G59" s="3">
-        <v>6500</v>
+        <v>6000</v>
       </c>
       <c r="H59" s="3">
-        <v>3600</v>
+        <v>5000</v>
       </c>
       <c r="I59" s="3">
-        <v>3300</v>
+        <v>2000</v>
       </c>
       <c r="J59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K59" s="3">
         <v>3100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2100</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4144,62 +4281,65 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E60" s="3">
         <v>5400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>4300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3500</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,8 +4358,11 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4260,7 +4403,7 @@
         <v>0</v>
       </c>
       <c r="P61" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Q61" s="3">
         <v>1000</v>
@@ -4269,7 +4412,7 @@
         <v>1000</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
@@ -4292,31 +4435,34 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
-      </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
-        <v>0</v>
-      </c>
-      <c r="G62" s="3">
-        <v>0</v>
-      </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -4366,8 +4512,11 @@
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4440,8 +4589,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4514,8 +4666,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4588,62 +4743,65 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E66" s="3">
         <v>5400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3600</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4662,8 +4820,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4690,8 +4851,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4764,8 +4926,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4838,8 +5003,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4912,8 +5080,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4986,62 +5157,65 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-68200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-66200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-62800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-59500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-55000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-49000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-45900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-44400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-41400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-33700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-27800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-22700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-18600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-15400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-13000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-10600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-8200</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5060,8 +5234,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5134,8 +5311,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5208,8 +5388,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5282,62 +5465,65 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E76" s="3">
         <v>-2800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>12300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>26900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>32600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>37500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>41500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>9600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-4200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-2700</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5356,8 +5542,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5430,73 +5619,76 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5509,68 +5701,71 @@
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-3500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-3100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-3000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-5900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-4300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-3300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1600</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5583,8 +5778,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5611,31 +5809,32 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -5685,8 +5884,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5759,8 +5961,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5833,8 +6038,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5907,8 +6115,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5981,8 +6192,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6055,62 +6269,65 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-1600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-4700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-4900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-3100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-600</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6129,8 +6346,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6157,31 +6377,32 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -6231,8 +6452,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6305,8 +6529,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6379,31 +6606,34 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3">
         <v>0</v>
@@ -6453,8 +6683,11 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6481,31 +6714,32 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6555,8 +6789,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6629,8 +6866,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6703,8 +6943,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6777,20 +7020,23 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E100" s="3">
         <v>1600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>500</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6800,8 +7046,8 @@
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3">
         <v>0</v>
@@ -6813,26 +7059,26 @@
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>36000</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>15300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1000</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6851,31 +7097,34 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6925,62 +7174,65 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-1900</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-7300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>31200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>12200</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
         <v>400</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6997,6 +7249,9 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/VRPX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VRPX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="92">
   <si>
     <t>VRPX</t>
   </si>
@@ -656,106 +656,106 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
@@ -768,8 +768,11 @@
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -794,8 +797,8 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -845,8 +848,11 @@
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -922,8 +928,11 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -999,8 +1008,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1028,8 +1040,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1037,62 +1050,62 @@
         <v>1100</v>
       </c>
       <c r="E12" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F12" s="3">
         <v>2000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>2800</v>
-      </c>
-      <c r="M12" s="3">
-        <v>3300</v>
       </c>
       <c r="N12" s="3">
         <v>3300</v>
       </c>
       <c r="O12" s="3">
-        <v>1700</v>
+        <v>3300</v>
       </c>
       <c r="P12" s="3">
         <v>1700</v>
       </c>
       <c r="Q12" s="3">
+        <v>1700</v>
+      </c>
+      <c r="R12" s="3">
         <v>300</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1300</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>300</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>200</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1105,8 +1118,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1182,8 +1198,11 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1196,21 +1215,21 @@
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>3800</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>-1300</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1250,8 +1269,8 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
@@ -1259,8 +1278,11 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1336,8 +1358,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1362,71 +1387,72 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E17" s="3">
         <v>1900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3300</v>
       </c>
-      <c r="G17" s="3">
-        <v>900</v>
-      </c>
       <c r="H17" s="3">
+        <v>4700</v>
+      </c>
+      <c r="I17" s="3">
         <v>6100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3200</v>
-      </c>
-      <c r="Q17" s="3">
-        <v>2300</v>
       </c>
       <c r="R17" s="3">
         <v>2300</v>
       </c>
       <c r="S17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="T17" s="3">
         <v>4200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1500</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1439,71 +1465,74 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-3500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3300</v>
       </c>
-      <c r="G18" s="3">
-        <v>-900</v>
-      </c>
       <c r="H18" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="I18" s="3">
         <v>-6100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-3200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-2900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-3100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-5900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-5100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-3200</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>-2300</v>
       </c>
       <c r="R18" s="3">
         <v>-2300</v>
       </c>
       <c r="S18" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="T18" s="3">
         <v>-4200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-1800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-3200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-1500</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1516,8 +1545,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1545,8 +1577,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1557,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
         <v>-100</v>
@@ -1572,13 +1605,13 @@
         <v>-100</v>
       </c>
       <c r="K20" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1587,11 +1620,11 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1607,8 +1640,8 @@
       <c r="V20" s="3">
         <v>0</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
+      <c r="W20" s="3">
+        <v>0</v>
       </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
@@ -1622,35 +1655,38 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-1900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-3400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-3200</v>
       </c>
-      <c r="G21" s="3">
-        <v>-800</v>
-      </c>
       <c r="H21" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="I21" s="3">
         <v>-6000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-3100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2800</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1699,19 +1735,22 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
+      <c r="F22" s="3">
+        <v>0</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
@@ -1725,8 +1764,8 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1737,11 +1776,11 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1750,7 +1789,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T22" s="3">
         <v>100</v>
@@ -1761,8 +1800,8 @@
       <c r="V22" s="3">
         <v>100</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
+      <c r="W22" s="3">
+        <v>100</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
@@ -1776,71 +1815,74 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-3500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-3200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-4600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-7600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-4300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-1600</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1853,8 +1895,11 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1879,8 +1924,8 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1930,8 +1975,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2007,71 +2055,74 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-3500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-3200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-4600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-3100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-3000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-4100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-4300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-3300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-1600</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2084,71 +2135,74 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-3500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-3200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-3100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-3000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-4100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-4300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-1600</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2161,8 +2215,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2238,8 +2295,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2315,8 +2375,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2392,8 +2455,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2469,8 +2535,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2481,7 +2550,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
         <v>100</v>
@@ -2496,13 +2565,13 @@
         <v>100</v>
       </c>
       <c r="K32" s="3">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -2511,11 +2580,11 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -2531,8 +2600,8 @@
       <c r="V32" s="3">
         <v>0</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
+      <c r="W32" s="3">
+        <v>0</v>
       </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
@@ -2546,71 +2615,74 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-3500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-3200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-3100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-3000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-4300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-3300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-1600</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2623,8 +2695,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2700,71 +2775,74 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-3500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-3200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-3100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-3000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-4300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-3300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-1600</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2777,76 +2855,79 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2859,8 +2940,11 @@
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2888,8 +2972,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2917,65 +3002,66 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="E41" s="3">
-        <v>1900</v>
+        <v>0</v>
       </c>
       <c r="F41" s="3">
         <v>1900</v>
       </c>
       <c r="G41" s="3">
+        <v>1900</v>
+      </c>
+      <c r="H41" s="3">
         <v>9100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>17000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>19000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>20600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>26100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>30800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>36800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>41700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>10500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>12300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>400</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2994,8 +3080,11 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3071,17 +3160,20 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3">
         <v>100</v>
       </c>
-      <c r="E43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3097,8 +3189,8 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -3125,11 +3217,11 @@
         <v>0</v>
       </c>
       <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
         <v>400</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3148,8 +3240,11 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3174,8 +3269,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3225,64 +3320,67 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E45" s="3">
         <v>100</v>
       </c>
       <c r="F45" s="3">
+        <v>100</v>
+      </c>
+      <c r="G45" s="3">
         <v>500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>400</v>
       </c>
       <c r="I45" s="3">
         <v>400</v>
       </c>
       <c r="J45" s="3">
+        <v>400</v>
+      </c>
+      <c r="K45" s="3">
         <v>500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1000</v>
       </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
       <c r="T45" s="3">
         <v>0</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
+      <c r="U45" s="3">
+        <v>0</v>
       </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
@@ -3302,65 +3400,68 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E46" s="3">
         <v>300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>16000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>18500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>19700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>23600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>29400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>34700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>39600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>43300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>11400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>13200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>800</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3379,8 +3480,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3405,8 +3509,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3456,8 +3560,11 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3482,8 +3589,8 @@
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
+      <c r="K48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L48" s="3">
         <v>0</v>
@@ -3533,8 +3640,11 @@
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3610,8 +3720,11 @@
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3687,8 +3800,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3764,8 +3880,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3790,8 +3909,8 @@
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
+      <c r="K52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -3808,21 +3927,21 @@
       <c r="P52" s="3">
         <v>0</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3">
-        <v>0</v>
+      <c r="Q52" s="3">
+        <v>0</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S52" s="3">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
         <v>400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>100</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3841,8 +3960,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3918,65 +4040,68 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E54" s="3">
         <v>300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>18500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>19700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>23600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>29400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>34700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>39600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>43300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>11400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>13200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>900</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3995,8 +4120,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4024,8 +4152,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4053,19 +4182,20 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E57" s="3">
         <v>100</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G57" s="3">
         <v>0</v>
@@ -4074,19 +4204,19 @@
         <v>0</v>
       </c>
       <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3">
         <v>100</v>
       </c>
-      <c r="J57" s="3">
-        <v>0</v>
-      </c>
       <c r="K57" s="3">
         <v>0</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
+      <c r="M57" s="3">
+        <v>0</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
@@ -4094,11 +4224,11 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>0</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
@@ -4115,8 +4245,8 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W57" s="3">
-        <v>0</v>
+      <c r="W57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X57" s="3">
         <v>0</v>
@@ -4130,8 +4260,11 @@
       <c r="AA57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4175,20 +4308,20 @@
         <v>0</v>
       </c>
       <c r="Q58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R58" s="3">
         <v>100</v>
       </c>
       <c r="S58" s="3">
+        <v>100</v>
+      </c>
+      <c r="T58" s="3">
         <v>500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1500</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4207,65 +4340,68 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E59" s="3">
-        <v>2500</v>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F59" s="3">
         <v>2500</v>
       </c>
       <c r="G59" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H59" s="3">
         <v>6000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5000</v>
-      </c>
-      <c r="I59" s="3">
-        <v>2000</v>
       </c>
       <c r="J59" s="3">
         <v>2000</v>
       </c>
       <c r="K59" s="3">
+        <v>2000</v>
+      </c>
+      <c r="L59" s="3">
         <v>3100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2100</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4284,65 +4420,68 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E60" s="3">
         <v>2400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>4300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3500</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4361,8 +4500,11 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4406,7 +4548,7 @@
         <v>0</v>
       </c>
       <c r="Q61" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="R61" s="3">
         <v>1000</v>
@@ -4415,7 +4557,7 @@
         <v>1000</v>
       </c>
       <c r="T61" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="U61" s="3">
         <v>0</v>
@@ -4438,8 +4580,11 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4464,8 +4609,8 @@
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
@@ -4515,8 +4660,11 @@
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4592,8 +4740,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4669,8 +4820,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4746,65 +4900,68 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>3600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>4700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3600</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4823,8 +4980,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4852,8 +5012,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4929,8 +5090,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5006,8 +5170,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5083,8 +5250,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5160,65 +5330,68 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-71600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-68200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-66200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-62800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-59500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-55000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-49000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-45900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-44400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-41400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-33700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-27800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-22700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-18600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-15400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-13000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-10600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-8200</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5237,8 +5410,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5314,8 +5490,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5391,8 +5570,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5468,65 +5650,68 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E76" s="3">
         <v>-2100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-2800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>12300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>26900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>32600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>37500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>41500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>9600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-4200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-2700</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5545,8 +5730,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5622,76 +5810,79 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5704,71 +5895,74 @@
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-3500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-3200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-3100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-3000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-4300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-3300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-1600</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5781,8 +5975,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5810,8 +6007,9 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5836,8 +6034,8 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L83" s="3">
         <v>0</v>
@@ -5887,8 +6085,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5964,8 +6165,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6041,8 +6245,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6118,8 +6325,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6195,8 +6405,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6272,65 +6485,68 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-1600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-3000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-4700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-6000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-4900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-3100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-600</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6349,8 +6565,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6378,8 +6597,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6404,8 +6624,8 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
@@ -6455,8 +6675,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6532,8 +6755,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6609,8 +6835,11 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6635,8 +6864,8 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L94" s="3">
         <v>0</v>
@@ -6686,8 +6915,11 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6715,8 +6947,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6741,8 +6974,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6792,8 +7025,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6869,8 +7105,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6946,8 +7185,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7023,23 +7265,26 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E100" s="3">
         <v>2600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>500</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7049,8 +7294,8 @@
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L100" s="3">
         <v>0</v>
@@ -7062,26 +7307,26 @@
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>36000</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>15300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1000</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7100,8 +7345,11 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7126,8 +7374,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -7177,65 +7425,68 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1900</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-7300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>31200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>12200</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>400</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7252,6 +7503,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
